--- a/JIRA/Planilha Sprint 258.xlsx
+++ b/JIRA/Planilha Sprint 258.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tke-my.sharepoint.com/personal/giovani_mesquita_tkelevator_com/Documents/Documents/jira/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="607" documentId="11_C8EDE477932071F27BFC503B19DFC79B3B8AE263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2978C6F-4F0E-4B99-9E6E-CAE849E64FF6}"/>
+  <xr:revisionPtr revIDLastSave="631" documentId="11_C8EDE477932071F27BFC503B19DFC79B3B8AE263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FEDC1C1-E28C-4945-8AC9-E398607CECBA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="660" windowWidth="19440" windowHeight="14880" tabRatio="458" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="660" windowWidth="19440" windowHeight="14880" tabRatio="458" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="226">
   <si>
     <t>Projeto</t>
   </si>
@@ -1261,6 +1261,15 @@
   </si>
   <si>
     <t>Analisar de depreciação de interfaces</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>AMS</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1401,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1434,12 +1443,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBFBFBF"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1528,32 +1543,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
     <border diagonalUp="1">
       <left/>
       <right style="thin">
@@ -1566,83 +1555,6 @@
       <diagonal style="medium">
         <color rgb="FF000000"/>
       </diagonal>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1825,7 +1737,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1848,9 +1760,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1908,93 +1818,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2004,7 +1835,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2016,62 +1874,91 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2099,83 +1986,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <border>
@@ -2311,33 +2121,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela3" displayName="Tabela3" ref="B2:B6" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela3" displayName="Tabela3" ref="B2:B6" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B2:B6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tipos Jira" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tipos Jira" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela7" displayName="Tabela7" ref="D2:D12" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela7" displayName="Tabela7" ref="D2:D12" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="D2:D12" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Etapa Jira" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Etapa Jira" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela9" displayName="Tabela9" ref="F2:G10" totalsRowShown="0">
-  <autoFilter ref="F2:G10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:G10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela9" displayName="Tabela9" ref="F2:H10" totalsRowShown="0">
+  <autoFilter ref="F2:H10" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:H10">
     <sortCondition ref="F2:F10"/>
   </sortState>
-  <tableColumns count="2">
+  <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Pessoas"/>
+    <tableColumn id="3" xr3:uid="{2F87785A-04EA-44AB-8A0F-4B13FC886B51}" name="Role"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="UUID Jira"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2345,8 +2156,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7E553FE5-137D-426F-91B4-E7A575DB3AB6}" name="Tabela5" displayName="Tabela5" ref="I2:J5" totalsRowShown="0">
-  <autoFilter ref="I2:J5" xr:uid="{7E553FE5-137D-426F-91B4-E7A575DB3AB6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7E553FE5-137D-426F-91B4-E7A575DB3AB6}" name="Tabela5" displayName="Tabela5" ref="J2:K5" totalsRowShown="0">
+  <autoFilter ref="J2:K5" xr:uid="{7E553FE5-137D-426F-91B4-E7A575DB3AB6}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{CD41D121-B677-4CFF-AD2A-FDF843C61FD9}" name="Tipos"/>
     <tableColumn id="2" xr3:uid="{1E5C5036-5065-4FDA-BCC8-A66E97F4123F}" name="Descrição"/>
@@ -2356,11 +2167,11 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5B7F3081-3EE6-4817-B664-0976AF736651}" name="Tabela4" displayName="Tabela4" ref="L2:M9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" tableBorderDxfId="4">
-  <autoFilter ref="L2:M9" xr:uid="{5B7F3081-3EE6-4817-B664-0976AF736651}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5B7F3081-3EE6-4817-B664-0976AF736651}" name="Tabela4" displayName="Tabela4" ref="M2:N9" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="M2:N9" xr:uid="{5B7F3081-3EE6-4817-B664-0976AF736651}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EB6FEAA2-E68A-4227-A64B-14D39A5D26CD}" name="Horas" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{53117B13-CDE6-469E-80F7-CE70D2EF0364}" name="Pontos" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{EB6FEAA2-E68A-4227-A64B-14D39A5D26CD}" name="Horas" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{53117B13-CDE6-469E-80F7-CE70D2EF0364}" name="Pontos" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2718,211 +2529,211 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="54" t="s">
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="53" t="s">
+      <c r="J1" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="57" t="s">
+      <c r="L1" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="M1" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="53" t="s">
+      <c r="N1" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="57" t="s">
+      <c r="O1" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="53" t="s">
+      <c r="P1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="53" t="s">
+      <c r="Q1" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="17" t="s">
+      <c r="S1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="17" t="s">
+      <c r="T1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="17" t="s">
+      <c r="U1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="17" t="s">
+      <c r="V1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="44" t="s">
+      <c r="W1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="90" t="s">
+      <c r="X1" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="90"/>
-      <c r="Z1" s="90"/>
-      <c r="AA1" s="90"/>
-      <c r="AB1" s="90"/>
-      <c r="AC1" s="47" t="s">
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="18" t="s">
+      <c r="AD1" s="16" t="s">
         <v>7</v>
       </c>
       <c r="AE1" s="12" t="str">
-        <f>Parâmetros!$I3</f>
+        <f>Parâmetros!$J3</f>
         <v>BL</v>
       </c>
       <c r="AF1" s="12" t="str">
-        <f>Parâmetros!$I4</f>
+        <f>Parâmetros!$J4</f>
         <v>CR</v>
       </c>
       <c r="AG1" s="12" t="str">
-        <f>Parâmetros!$I5</f>
+        <f>Parâmetros!$J5</f>
         <v>MP</v>
       </c>
       <c r="AH1" s="12" t="str">
-        <f>Parâmetros!$I3</f>
+        <f>Parâmetros!$J3</f>
         <v>BL</v>
       </c>
       <c r="AI1" s="12" t="str">
-        <f>Parâmetros!$I4</f>
+        <f>Parâmetros!$J4</f>
         <v>CR</v>
       </c>
       <c r="AJ1" s="12" t="str">
-        <f>Parâmetros!$I5</f>
+        <f>Parâmetros!$J5</f>
         <v>MP</v>
       </c>
       <c r="AK1" s="12" t="str">
-        <f>Parâmetros!$I3</f>
+        <f>Parâmetros!$J3</f>
         <v>BL</v>
       </c>
       <c r="AL1" s="12" t="str">
-        <f>Parâmetros!$I4</f>
+        <f>Parâmetros!$J4</f>
         <v>CR</v>
       </c>
       <c r="AM1" s="12" t="str">
-        <f>Parâmetros!$I5</f>
+        <f>Parâmetros!$J5</f>
         <v>MP</v>
       </c>
     </row>
     <row r="2" spans="1:39" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="str">
+      <c r="A2" s="17" t="str">
         <f t="shared" ref="A2:A20" si="0">UPPER(LEFT(I2, 3))</f>
         <v>ENS</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="21">
-        <v>0</v>
-      </c>
-      <c r="D2" s="21">
-        <v>0</v>
-      </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23">
-        <v>0</v>
-      </c>
-      <c r="G2" s="21" t="s">
+      <c r="C2" s="19">
+        <v>0</v>
+      </c>
+      <c r="D2" s="19">
+        <v>0</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21">
+        <v>0</v>
+      </c>
+      <c r="G2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="21" t="str">
+      <c r="K2" s="19" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J2,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="21" t="str">
+      <c r="M2" s="19" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$L2,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:4a0c9d58-dbcd-4acf-b9ef-a74bff31dc8e</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="27">
+      <c r="S2" s="25">
         <v>10</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="26">
         <f>_xlfn.XLOOKUP(S2,Tabela4[Horas],Tabela4[Pontos],,1)</f>
         <v>1</v>
       </c>
-      <c r="U2" s="21" t="s">
+      <c r="U2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="21"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="65" t="str">
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="73" t="str">
         <f t="shared" ref="Y2:Y20" si="1">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; U2,U2)</f>
         <v>ENS-10640</v>
       </c>
-      <c r="Z2" s="65">
+      <c r="Z2" s="73">
         <f t="shared" ref="Z2:Z20" si="2">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V2,V2)</f>
         <v>0</v>
       </c>
-      <c r="AA2" s="65">
+      <c r="AA2" s="73">
         <f t="shared" ref="AA2:AA20" si="3">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; W2,W2)</f>
         <v>0</v>
       </c>
-      <c r="AB2" s="64"/>
-      <c r="AC2" s="48" t="s">
+      <c r="AB2" s="72"/>
+      <c r="AC2" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" s="29" t="s">
+      <c r="AD2" s="27" t="s">
         <v>35</v>
       </c>
       <c r="AE2" s="4" t="b">
@@ -2963,89 +2774,89 @@
       </c>
     </row>
     <row r="3" spans="1:39" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="str">
+      <c r="A3" s="17" t="str">
         <f t="shared" ref="A3" si="7">UPPER(LEFT(I3, 3))</f>
         <v>ENS</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23">
-        <v>0</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="E3" s="20"/>
+      <c r="F3" s="21">
+        <v>0</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="21" t="str">
+      <c r="K3" s="19" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J3,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="21" t="str">
+      <c r="M3" s="19" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$L3,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:4d5b2de5-c33f-44cb-8545-f17228d08baf</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="P3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="Q3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="R3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="S3" s="27">
+      <c r="S3" s="25">
         <v>1</v>
       </c>
-      <c r="T3" s="28">
+      <c r="T3" s="26">
         <f>_xlfn.XLOOKUP(S3,Tabela4[Horas],Tabela4[Pontos],,1)</f>
         <v>0.5</v>
       </c>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="64"/>
-      <c r="Y3" s="65">
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="73">
         <f t="shared" ref="Y3" si="8">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; U3,U3)</f>
         <v>0</v>
       </c>
-      <c r="Z3" s="65">
+      <c r="Z3" s="73">
         <f t="shared" ref="Z3" si="9">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V3,V3)</f>
         <v>0</v>
       </c>
-      <c r="AA3" s="65">
+      <c r="AA3" s="73">
         <f t="shared" ref="AA3" si="10">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; W3,W3)</f>
         <v>0</v>
       </c>
-      <c r="AB3" s="64"/>
-      <c r="AC3" s="48" t="s">
+      <c r="AB3" s="72"/>
+      <c r="AC3" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="AD3" s="29" t="s">
+      <c r="AD3" s="27" t="s">
         <v>41</v>
       </c>
       <c r="AE3" s="4" t="b">
@@ -3086,11 +2897,11 @@
       </c>
     </row>
     <row r="4" spans="1:39" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="str">
+      <c r="A4" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="11">
@@ -3099,8 +2910,8 @@
       <c r="D4" s="11">
         <v>0</v>
       </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="33">
+      <c r="E4" s="30"/>
+      <c r="F4" s="31">
         <v>0</v>
       </c>
       <c r="G4" s="11" t="s">
@@ -3109,10 +2920,10 @@
       <c r="H4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="11" t="str">
@@ -3152,25 +2963,25 @@
         <v>44</v>
       </c>
       <c r="V4" s="11"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="64"/>
-      <c r="Y4" s="63" t="str">
+      <c r="W4" s="11"/>
+      <c r="X4" s="72"/>
+      <c r="Y4" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-8159</v>
       </c>
-      <c r="Z4" s="63">
+      <c r="Z4" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA4" s="63">
+      <c r="AA4" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB4" s="64"/>
-      <c r="AC4" s="49" t="s">
+      <c r="AB4" s="72"/>
+      <c r="AC4" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="AD4" s="37" t="s">
+      <c r="AD4" s="35" t="s">
         <v>45</v>
       </c>
       <c r="AE4" s="4" t="str">
@@ -3211,11 +3022,11 @@
       </c>
     </row>
     <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="str">
+      <c r="A5" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="11">
@@ -3224,27 +3035,27 @@
       <c r="D5" s="11">
         <v>0</v>
       </c>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38">
+      <c r="E5" s="36"/>
+      <c r="F5" s="36">
         <v>0</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K5" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J5,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="L5" s="33" t="s">
         <v>42</v>
       </c>
       <c r="M5" s="11" t="str">
@@ -3263,10 +3074,10 @@
       <c r="Q5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="39" t="s">
+      <c r="R5" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="36">
+      <c r="S5" s="34">
         <v>4</v>
       </c>
       <c r="T5" s="11">
@@ -3277,25 +3088,25 @@
         <v>48</v>
       </c>
       <c r="V5" s="11"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="64"/>
-      <c r="Y5" s="63" t="str">
+      <c r="W5" s="11"/>
+      <c r="X5" s="72"/>
+      <c r="Y5" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9017</v>
       </c>
-      <c r="Z5" s="63">
+      <c r="Z5" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA5" s="63">
+      <c r="AA5" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB5" s="62"/>
-      <c r="AC5" s="50" t="s">
+      <c r="AB5" s="43"/>
+      <c r="AC5" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD5" s="40" t="s">
+      <c r="AD5" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE5" s="4" t="str">
@@ -3336,40 +3147,40 @@
       </c>
     </row>
     <row r="6" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="str">
+      <c r="A6" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="28" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38">
+      <c r="E6" s="36"/>
+      <c r="F6" s="36">
         <v>0</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K6" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J6,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L6" s="35" t="s">
+      <c r="L6" s="33" t="s">
         <v>51</v>
       </c>
       <c r="M6" s="11" t="str">
@@ -3385,13 +3196,13 @@
       <c r="P6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="Q6" s="35" t="s">
+      <c r="Q6" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="R6" s="41" t="s">
+      <c r="R6" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="S6" s="36">
+      <c r="S6" s="34">
         <v>2</v>
       </c>
       <c r="T6" s="11">
@@ -3402,25 +3213,25 @@
         <v>54</v>
       </c>
       <c r="V6" s="11"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="64"/>
-      <c r="Y6" s="63" t="str">
+      <c r="W6" s="11"/>
+      <c r="X6" s="72"/>
+      <c r="Y6" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-8908</v>
       </c>
-      <c r="Z6" s="63">
+      <c r="Z6" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA6" s="63">
+      <c r="AA6" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB6" s="62"/>
-      <c r="AC6" s="50" t="s">
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD6" s="40" t="s">
+      <c r="AD6" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE6" s="4" t="str">
@@ -3461,11 +3272,11 @@
       </c>
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="str">
+      <c r="A7" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="11">
@@ -3481,20 +3292,20 @@
       <c r="G7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="35" t="s">
+      <c r="H7" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="35" t="s">
+      <c r="J7" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K7" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J7,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L7" s="35" t="s">
+      <c r="L7" s="33" t="s">
         <v>42</v>
       </c>
       <c r="M7" s="11" t="str">
@@ -3513,7 +3324,7 @@
       <c r="Q7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R7" s="39" t="s">
+      <c r="R7" s="37" t="s">
         <v>57</v>
       </c>
       <c r="S7" s="10">
@@ -3527,25 +3338,25 @@
         <v>58</v>
       </c>
       <c r="V7" s="11"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="62"/>
-      <c r="Y7" s="63" t="str">
+      <c r="W7" s="11"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9944</v>
       </c>
-      <c r="Z7" s="63">
+      <c r="Z7" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA7" s="63">
+      <c r="AA7" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB7" s="62"/>
-      <c r="AC7" s="50" t="s">
+      <c r="AB7" s="43"/>
+      <c r="AC7" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD7" s="40" t="s">
+      <c r="AD7" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE7" s="4" t="str">
@@ -3586,11 +3397,11 @@
       </c>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="str">
+      <c r="A8" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="11">
@@ -3606,20 +3417,20 @@
       <c r="G8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J8,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L8" s="35" t="s">
+      <c r="L8" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M8" s="11" t="str">
@@ -3638,7 +3449,7 @@
       <c r="Q8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R8" s="39" t="s">
+      <c r="R8" s="37" t="s">
         <v>57</v>
       </c>
       <c r="S8" s="10">
@@ -3652,25 +3463,25 @@
         <v>58</v>
       </c>
       <c r="V8" s="11"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="62"/>
-      <c r="Y8" s="63" t="str">
+      <c r="W8" s="11"/>
+      <c r="X8" s="43"/>
+      <c r="Y8" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9944</v>
       </c>
-      <c r="Z8" s="63">
+      <c r="Z8" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA8" s="63">
+      <c r="AA8" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB8" s="62"/>
-      <c r="AC8" s="50" t="s">
+      <c r="AB8" s="43"/>
+      <c r="AC8" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD8" s="40" t="s">
+      <c r="AD8" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE8" s="4" t="str">
@@ -3711,11 +3522,11 @@
       </c>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="str">
+      <c r="A9" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="11">
@@ -3731,20 +3542,20 @@
       <c r="G9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="I9" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K9" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J9,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L9" s="35" t="s">
+      <c r="L9" s="33" t="s">
         <v>51</v>
       </c>
       <c r="M9" s="11" t="str">
@@ -3763,7 +3574,7 @@
       <c r="Q9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R9" s="39" t="s">
+      <c r="R9" s="37" t="s">
         <v>57</v>
       </c>
       <c r="S9" s="10">
@@ -3777,25 +3588,25 @@
         <v>58</v>
       </c>
       <c r="V9" s="11"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="62"/>
-      <c r="Y9" s="63" t="str">
+      <c r="W9" s="11"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9944</v>
       </c>
-      <c r="Z9" s="63">
+      <c r="Z9" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA9" s="63">
+      <c r="AA9" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB9" s="62"/>
-      <c r="AC9" s="50" t="s">
+      <c r="AB9" s="43"/>
+      <c r="AC9" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD9" s="40" t="s">
+      <c r="AD9" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE9" s="4" t="str">
@@ -3836,11 +3647,11 @@
       </c>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="str">
+      <c r="A10" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -3856,20 +3667,20 @@
       <c r="G10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="I10" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K10" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J10,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L10" s="35" t="s">
+      <c r="L10" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M10" s="11" t="str">
@@ -3885,10 +3696,10 @@
       <c r="P10" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="Q10" s="35" t="s">
+      <c r="Q10" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="R10" s="39" t="s">
+      <c r="R10" s="37" t="s">
         <v>65</v>
       </c>
       <c r="S10" s="10">
@@ -3902,25 +3713,25 @@
         <v>66</v>
       </c>
       <c r="V10" s="11"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="63" t="str">
+      <c r="W10" s="11"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9951</v>
       </c>
-      <c r="Z10" s="63">
+      <c r="Z10" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA10" s="63">
+      <c r="AA10" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB10" s="62"/>
-      <c r="AC10" s="50" t="s">
+      <c r="AB10" s="43"/>
+      <c r="AC10" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD10" s="40" t="s">
+      <c r="AD10" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE10" s="4" t="str">
@@ -3961,56 +3772,56 @@
       </c>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="58" t="str">
+      <c r="A11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51">
-        <v>0</v>
-      </c>
-      <c r="G11" s="51" t="s">
+      <c r="E11" s="11"/>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="51" t="s">
+      <c r="H11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="59" t="s">
+      <c r="I11" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="60" t="s">
+      <c r="J11" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="51" t="str">
+      <c r="K11" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J11,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L11" s="60" t="s">
+      <c r="L11" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="M11" s="51" t="str">
+      <c r="M11" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$L11,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>6245e14af6a26900695d5c1c</v>
       </c>
-      <c r="N11" s="51" t="s">
+      <c r="N11" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="O11" s="51" t="s">
+      <c r="O11" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="P11" s="51" t="s">
+      <c r="P11" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q11" s="60" t="s">
+      <c r="Q11" s="33" t="s">
         <v>64</v>
       </c>
       <c r="R11" s="11" t="s">
@@ -4027,25 +3838,25 @@
         <v>72</v>
       </c>
       <c r="V11" s="11"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="62"/>
-      <c r="Y11" s="63" t="str">
+      <c r="W11" s="11"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9954</v>
       </c>
-      <c r="Z11" s="63">
+      <c r="Z11" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="63">
+      <c r="AA11" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB11" s="62"/>
-      <c r="AC11" s="50" t="s">
+      <c r="AB11" s="43"/>
+      <c r="AC11" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD11" s="40" t="s">
+      <c r="AD11" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE11" s="4" t="str">
@@ -4086,33 +3897,33 @@
       </c>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="str">
+      <c r="A12" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="28" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38">
+      <c r="E12" s="36"/>
+      <c r="F12" s="36">
         <v>0</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="35" t="s">
+      <c r="J12" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K12" s="11" t="str">
@@ -4135,10 +3946,10 @@
       <c r="P12" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="Q12" s="35" t="s">
+      <c r="Q12" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="R12" s="39" t="s">
+      <c r="R12" s="37" t="s">
         <v>76</v>
       </c>
       <c r="S12" s="10">
@@ -4152,25 +3963,25 @@
         <v>77</v>
       </c>
       <c r="V12" s="11"/>
-      <c r="W12" s="46"/>
-      <c r="X12" s="62"/>
-      <c r="Y12" s="63" t="str">
+      <c r="W12" s="11"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9957</v>
       </c>
-      <c r="Z12" s="63">
+      <c r="Z12" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="63">
+      <c r="AA12" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="62"/>
-      <c r="AC12" s="50" t="s">
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD12" s="40" t="s">
+      <c r="AD12" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE12" s="4" t="str">
@@ -4211,11 +4022,11 @@
       </c>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="str">
+      <c r="A13" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="11">
@@ -4231,20 +4042,20 @@
       <c r="G13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="35" t="s">
+      <c r="H13" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="34" t="s">
+      <c r="I13" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="35" t="s">
+      <c r="J13" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K13" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J13,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L13" s="35" t="s">
+      <c r="L13" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M13" s="11" t="str">
@@ -4260,10 +4071,10 @@
       <c r="P13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="Q13" s="35" t="s">
+      <c r="Q13" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R13" s="39" t="s">
+      <c r="R13" s="37" t="s">
         <v>47</v>
       </c>
       <c r="S13" s="10">
@@ -4277,25 +4088,25 @@
         <v>80</v>
       </c>
       <c r="V13" s="11"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="62"/>
-      <c r="Y13" s="63" t="str">
+      <c r="W13" s="11"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9632</v>
       </c>
-      <c r="Z13" s="63">
+      <c r="Z13" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA13" s="63">
+      <c r="AA13" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB13" s="62"/>
-      <c r="AC13" s="50" t="s">
+      <c r="AB13" s="43"/>
+      <c r="AC13" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD13" s="40" t="s">
+      <c r="AD13" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE13" s="4" t="str">
@@ -4336,59 +4147,59 @@
       </c>
     </row>
     <row r="14" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="str">
+      <c r="A14" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="51">
-        <v>0</v>
-      </c>
-      <c r="D14" s="51">
-        <v>0</v>
-      </c>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51">
-        <v>0</v>
-      </c>
-      <c r="G14" s="51" t="s">
+      <c r="C14" s="11">
+        <v>0</v>
+      </c>
+      <c r="D14" s="11">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="60" t="s">
+      <c r="H14" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="59" t="s">
+      <c r="I14" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="60" t="s">
+      <c r="J14" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="51" t="str">
+      <c r="K14" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J14,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L14" s="60" t="s">
+      <c r="L14" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="M14" s="51" t="str">
+      <c r="M14" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$L14,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>6245e14af6a26900695d5c1c</v>
       </c>
-      <c r="N14" s="51" t="s">
+      <c r="N14" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="O14" s="51" t="s">
+      <c r="O14" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="P14" s="51" t="s">
+      <c r="P14" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="Q14" s="60" t="s">
+      <c r="Q14" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R14" s="39" t="s">
+      <c r="R14" s="37" t="s">
         <v>47</v>
       </c>
       <c r="S14" s="10">
@@ -4402,25 +4213,25 @@
         <v>82</v>
       </c>
       <c r="V14" s="11"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="63" t="str">
+      <c r="W14" s="11"/>
+      <c r="X14" s="43"/>
+      <c r="Y14" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-9635</v>
       </c>
-      <c r="Z14" s="63">
+      <c r="Z14" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="63">
+      <c r="AA14" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="62"/>
-      <c r="AC14" s="50" t="s">
+      <c r="AB14" s="43"/>
+      <c r="AC14" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD14" s="40" t="s">
+      <c r="AD14" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE14" s="4" t="str">
@@ -4461,59 +4272,59 @@
       </c>
     </row>
     <row r="15" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="str">
+      <c r="A15" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51">
-        <v>0</v>
-      </c>
-      <c r="G15" s="51" t="s">
+      <c r="E15" s="11"/>
+      <c r="F15" s="11">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="60" t="s">
+      <c r="H15" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="59" t="s">
+      <c r="I15" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="60" t="s">
+      <c r="J15" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="51" t="str">
+      <c r="K15" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J15,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L15" s="60" t="s">
+      <c r="L15" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="M15" s="51" t="str">
+      <c r="M15" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$L15,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>6245e14af6a26900695d5c1c</v>
       </c>
-      <c r="N15" s="51" t="s">
+      <c r="N15" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="O15" s="51" t="s">
+      <c r="O15" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="P15" s="51" t="s">
+      <c r="P15" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="Q15" s="60" t="s">
+      <c r="Q15" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="R15" s="39" t="s">
+      <c r="R15" s="37" t="s">
         <v>47</v>
       </c>
       <c r="S15" s="10">
@@ -4527,25 +4338,25 @@
         <v>86</v>
       </c>
       <c r="V15" s="11"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="63" t="str">
+      <c r="W15" s="11"/>
+      <c r="X15" s="43"/>
+      <c r="Y15" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-10442</v>
       </c>
-      <c r="Z15" s="63">
+      <c r="Z15" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="63">
+      <c r="AA15" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB15" s="62"/>
-      <c r="AC15" s="50" t="s">
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD15" s="40" t="s">
+      <c r="AD15" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE15" s="4" t="str">
@@ -4586,11 +4397,11 @@
       </c>
     </row>
     <row r="16" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="str">
+      <c r="A16" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -4606,20 +4417,20 @@
       <c r="G16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="35" t="s">
+      <c r="H16" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="J16" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K16" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J16,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L16" s="35" t="s">
+      <c r="L16" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M16" s="11" t="str">
@@ -4635,10 +4446,10 @@
       <c r="P16" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="Q16" s="35" t="s">
+      <c r="Q16" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R16" s="39" t="s">
+      <c r="R16" s="37" t="s">
         <v>47</v>
       </c>
       <c r="S16" s="10">
@@ -4652,25 +4463,25 @@
         <v>90</v>
       </c>
       <c r="V16" s="11"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="63" t="str">
+      <c r="W16" s="11"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-10362</v>
       </c>
-      <c r="Z16" s="63">
+      <c r="Z16" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="63">
+      <c r="AA16" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="62"/>
-      <c r="AC16" s="50" t="s">
+      <c r="AB16" s="43"/>
+      <c r="AC16" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD16" s="40" t="s">
+      <c r="AD16" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE16" s="4" t="str">
@@ -4711,17 +4522,17 @@
       </c>
     </row>
     <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="str">
+      <c r="A17" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="42" t="s">
+      <c r="D17" s="40" t="s">
         <v>92</v>
       </c>
       <c r="E17" s="11"/>
@@ -4731,20 +4542,20 @@
       <c r="G17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="35" t="s">
+      <c r="H17" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I17" s="34" t="s">
+      <c r="I17" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="35" t="s">
+      <c r="J17" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K17" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J17,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L17" s="35" t="s">
+      <c r="L17" s="33" t="s">
         <v>51</v>
       </c>
       <c r="M17" s="11" t="str">
@@ -4757,13 +4568,13 @@
       <c r="O17" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="P17" s="43" t="s">
+      <c r="P17" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="Q17" s="35" t="s">
+      <c r="Q17" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R17" s="39" t="s">
+      <c r="R17" s="37" t="s">
         <v>94</v>
       </c>
       <c r="S17" s="10">
@@ -4777,25 +4588,25 @@
         <v>95</v>
       </c>
       <c r="V17" s="11"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="63" t="str">
+      <c r="W17" s="11"/>
+      <c r="X17" s="43"/>
+      <c r="Y17" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-10576</v>
       </c>
-      <c r="Z17" s="63">
+      <c r="Z17" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="63">
+      <c r="AA17" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="62"/>
-      <c r="AC17" s="50" t="s">
+      <c r="AB17" s="43"/>
+      <c r="AC17" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD17" s="40" t="s">
+      <c r="AD17" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE17" s="4" t="str">
@@ -4836,59 +4647,59 @@
       </c>
     </row>
     <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="58" t="str">
+      <c r="A18" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51">
-        <v>0</v>
-      </c>
-      <c r="G18" s="51" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="60" t="s">
+      <c r="H18" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="59" t="s">
+      <c r="I18" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J18" s="60" t="s">
+      <c r="J18" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="K18" s="51" t="str">
+      <c r="K18" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J18,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L18" s="60" t="s">
+      <c r="L18" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="M18" s="51" t="str">
+      <c r="M18" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$L18,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>6245e14af6a26900695d5c1c</v>
       </c>
-      <c r="N18" s="51" t="s">
+      <c r="N18" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="O18" s="51" t="s">
+      <c r="O18" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="P18" s="51" t="s">
+      <c r="P18" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="Q18" s="51" t="s">
+      <c r="Q18" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="R18" s="39" t="s">
+      <c r="R18" s="37" t="s">
         <v>99</v>
       </c>
       <c r="S18" s="10">
@@ -4902,25 +4713,25 @@
         <v>100</v>
       </c>
       <c r="V18" s="11"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="62"/>
-      <c r="Y18" s="63" t="str">
+      <c r="W18" s="11"/>
+      <c r="X18" s="43"/>
+      <c r="Y18" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-10673</v>
       </c>
-      <c r="Z18" s="63">
+      <c r="Z18" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA18" s="63">
+      <c r="AA18" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB18" s="62"/>
-      <c r="AC18" s="50" t="s">
+      <c r="AB18" s="43"/>
+      <c r="AC18" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD18" s="40" t="s">
+      <c r="AD18" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE18" s="4" t="str">
@@ -4961,11 +4772,11 @@
       </c>
     </row>
     <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="str">
+      <c r="A19" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="11">
@@ -4981,20 +4792,20 @@
       <c r="G19" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H19" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I19" s="34" t="s">
+      <c r="I19" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="35" t="s">
+      <c r="J19" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K19" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J19,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L19" s="35" t="s">
+      <c r="L19" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M19" s="11" t="str">
@@ -5013,7 +4824,7 @@
       <c r="Q19" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="R19" s="39" t="s">
+      <c r="R19" s="37" t="s">
         <v>102</v>
       </c>
       <c r="S19" s="10">
@@ -5027,25 +4838,25 @@
         <v>103</v>
       </c>
       <c r="V19" s="11"/>
-      <c r="W19" s="46"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="63" t="str">
+      <c r="W19" s="11"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-10676</v>
       </c>
-      <c r="Z19" s="63">
+      <c r="Z19" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="63">
+      <c r="AA19" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="62"/>
-      <c r="AC19" s="50" t="s">
+      <c r="AB19" s="43"/>
+      <c r="AC19" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD19" s="40" t="s">
+      <c r="AD19" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE19" s="4" t="str">
@@ -5086,11 +4897,11 @@
       </c>
     </row>
     <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="str">
+      <c r="A20" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ENS</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -5106,13 +4917,13 @@
       <c r="G20" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="H20" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K20" s="11" t="str">
@@ -5135,7 +4946,7 @@
       <c r="P20" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="Q20" s="35" t="s">
+      <c r="Q20" s="33" t="s">
         <v>32</v>
       </c>
       <c r="R20" s="11" t="s">
@@ -5152,25 +4963,25 @@
         <v>107</v>
       </c>
       <c r="V20" s="11"/>
-      <c r="W20" s="69"/>
-      <c r="X20" s="66"/>
-      <c r="Y20" s="67" t="str">
+      <c r="W20" s="11"/>
+      <c r="X20" s="43"/>
+      <c r="Y20" s="44" t="str">
         <f t="shared" si="1"/>
         <v>ENS-10380</v>
       </c>
-      <c r="Z20" s="67">
+      <c r="Z20" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="67">
+      <c r="AA20" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="66"/>
-      <c r="AC20" s="70" t="s">
+      <c r="AB20" s="43"/>
+      <c r="AC20" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AD20" s="71" t="s">
+      <c r="AD20" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AE20" s="4" t="str">
@@ -5211,11 +5022,11 @@
       </c>
     </row>
     <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="30" t="str">
+      <c r="A21" s="28" t="str">
         <f t="shared" ref="A21" si="11">UPPER(LEFT(I21, 3))</f>
         <v>ENS</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="11" t="s">
@@ -5231,20 +5042,20 @@
       <c r="G21" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H21" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I21" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K21" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J21,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L21" s="35" t="s">
+      <c r="L21" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M21" s="11" t="str">
@@ -5257,13 +5068,13 @@
       <c r="O21" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="P21" s="89" t="s">
+      <c r="P21" s="48" t="s">
         <v>111</v>
       </c>
       <c r="Q21" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="R21" s="39" t="s">
+      <c r="R21" s="37" t="s">
         <v>112</v>
       </c>
       <c r="S21" s="10">
@@ -5276,121 +5087,121 @@
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
-      <c r="X21" s="72"/>
-      <c r="Y21" s="73">
+      <c r="X21" s="43"/>
+      <c r="Y21" s="44">
         <f t="shared" ref="Y21" si="12">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; U21,U21)</f>
         <v>0</v>
       </c>
-      <c r="Z21" s="73">
+      <c r="Z21" s="44">
         <f t="shared" ref="Z21" si="13">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V21,V21)</f>
         <v>0</v>
       </c>
-      <c r="AA21" s="73">
+      <c r="AA21" s="44">
         <f t="shared" ref="AA21" si="14">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; W21,W21)</f>
         <v>0</v>
       </c>
-      <c r="AB21" s="72"/>
-      <c r="AC21" s="74" t="s">
+      <c r="AB21" s="43"/>
+      <c r="AC21" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="AD21" s="74" t="s">
+      <c r="AD21" s="45" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="75" t="s">
+      <c r="C22" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="68" t="s">
+      <c r="D22" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77">
-        <v>0</v>
-      </c>
-      <c r="G22" s="68" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="36">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H22" s="78" t="s">
+      <c r="H22" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I22" s="79" t="s">
+      <c r="I22" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J22" s="78" t="s">
+      <c r="J22" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="K22" s="68" t="str">
+      <c r="K22" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J22,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L22" s="80" t="s">
+      <c r="L22" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="M22" s="68" t="str">
+      <c r="M22" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$L22,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>557058:004709f9-0a88-4979-a875-f58ca3985cf7</v>
       </c>
-      <c r="N22" s="81" t="s">
+      <c r="N22" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="O22" s="68" t="s">
+      <c r="O22" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="P22" s="68" t="s">
+      <c r="P22" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="Q22" s="68" t="s">
+      <c r="Q22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="R22" s="82" t="s">
+      <c r="R22" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="S22" s="83">
+      <c r="S22" s="34">
         <v>4</v>
       </c>
       <c r="T22" s="11">
         <f>_xlfn.XLOOKUP(S22,Tabela4[Horas],Tabela4[Pontos],,1)</f>
         <v>0.5</v>
       </c>
-      <c r="U22" s="68" t="s">
+      <c r="U22" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="V22" s="68"/>
-      <c r="W22" s="68"/>
-      <c r="X22" s="84"/>
-      <c r="Y22" s="85" t="str">
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="46"/>
+      <c r="Y22" s="44" t="str">
         <f t="shared" ref="Y22" si="15">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; U22,U22)</f>
         <v>ENS-8650</v>
       </c>
-      <c r="Z22" s="85">
+      <c r="Z22" s="44">
         <f t="shared" ref="Z22" si="16">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V22,V22)</f>
         <v>0</v>
       </c>
-      <c r="AA22" s="85">
+      <c r="AA22" s="44">
         <f t="shared" ref="AA22" si="17">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; W22,W22)</f>
         <v>0</v>
       </c>
-      <c r="AB22" s="84"/>
-      <c r="AC22" s="86" t="s">
+      <c r="AB22" s="46"/>
+      <c r="AC22" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="AD22" s="86" t="s">
+      <c r="AD22" s="47" t="s">
         <v>45</v>
       </c>
       <c r="AE22" s="4"/>
     </row>
     <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C23" s="11">
@@ -5399,27 +5210,27 @@
       <c r="D23" s="11">
         <v>0</v>
       </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38">
+      <c r="E23" s="36"/>
+      <c r="F23" s="36">
         <v>0</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H23" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I23" s="34" t="s">
+      <c r="I23" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J23" s="35" t="s">
+      <c r="J23" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K23" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J23,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L23" s="43" t="s">
+      <c r="L23" s="41" t="s">
         <v>42</v>
       </c>
       <c r="M23" s="11" t="str">
@@ -5441,7 +5252,7 @@
       <c r="R23" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="S23" s="36">
+      <c r="S23" s="34">
         <v>6</v>
       </c>
       <c r="T23" s="11">
@@ -5451,32 +5262,32 @@
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
-      <c r="X23" s="87"/>
-      <c r="Y23" s="73">
+      <c r="X23" s="46"/>
+      <c r="Y23" s="44">
         <f t="shared" ref="Y23" si="18">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; U23,U23)</f>
         <v>0</v>
       </c>
-      <c r="Z23" s="73">
+      <c r="Z23" s="44">
         <f>HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V23,V23)</f>
         <v>0</v>
       </c>
-      <c r="AA23" s="73">
+      <c r="AA23" s="44">
         <f t="shared" ref="AA23" si="19">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; W23,W23)</f>
         <v>0</v>
       </c>
-      <c r="AB23" s="87"/>
-      <c r="AC23" s="88" t="s">
+      <c r="AB23" s="46"/>
+      <c r="AC23" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="AD23" s="88" t="s">
+      <c r="AD23" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="11">
@@ -5485,27 +5296,27 @@
       <c r="D24" s="11">
         <v>0</v>
       </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38">
+      <c r="E24" s="36"/>
+      <c r="F24" s="36">
         <v>0</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="34" t="s">
+      <c r="I24" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K24" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J24,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L24" s="43" t="s">
+      <c r="L24" s="41" t="s">
         <v>42</v>
       </c>
       <c r="M24" s="11" t="str">
@@ -5524,10 +5335,10 @@
       <c r="Q24" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R24" s="39" t="s">
+      <c r="R24" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S24" s="36">
+      <c r="S24" s="34">
         <v>2</v>
       </c>
       <c r="T24" s="11">
@@ -5537,30 +5348,30 @@
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
-      <c r="X24" s="87"/>
-      <c r="Y24" s="73">
+      <c r="X24" s="46"/>
+      <c r="Y24" s="44">
         <f t="shared" ref="Y24:Y25" si="20">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; U24,U24)</f>
         <v>0</v>
       </c>
-      <c r="Z24" s="73">
+      <c r="Z24" s="44">
         <f>HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V24,V24)</f>
         <v>0</v>
       </c>
-      <c r="AA24" s="73">
+      <c r="AA24" s="44">
         <f t="shared" ref="AA24:AA25" si="21">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; W24,W24)</f>
         <v>0</v>
       </c>
-      <c r="AB24" s="87"/>
-      <c r="AC24" s="88"/>
-      <c r="AD24" s="88" t="s">
+      <c r="AB24" s="46"/>
+      <c r="AC24" s="47"/>
+      <c r="AD24" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="11">
@@ -5569,27 +5380,27 @@
       <c r="D25" s="11">
         <v>0</v>
       </c>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38">
+      <c r="E25" s="36"/>
+      <c r="F25" s="36">
         <v>0</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="35" t="s">
+      <c r="H25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I25" s="34" t="s">
+      <c r="I25" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J25" s="35" t="s">
+      <c r="J25" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K25" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J25,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L25" s="43" t="s">
+      <c r="L25" s="41" t="s">
         <v>42</v>
       </c>
       <c r="M25" s="11" t="str">
@@ -5608,10 +5419,10 @@
       <c r="Q25" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R25" s="39" t="s">
+      <c r="R25" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S25" s="36">
+      <c r="S25" s="34">
         <v>2</v>
       </c>
       <c r="T25" s="11">
@@ -5621,30 +5432,30 @@
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
       <c r="W25" s="11"/>
-      <c r="X25" s="87"/>
-      <c r="Y25" s="73">
+      <c r="X25" s="46"/>
+      <c r="Y25" s="44">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Z25" s="73">
+      <c r="Z25" s="44">
         <f t="shared" ref="Z25" si="22">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V25,V25)</f>
         <v>0</v>
       </c>
-      <c r="AA25" s="73">
+      <c r="AA25" s="44">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="88"/>
-      <c r="AD25" s="88" t="s">
+      <c r="AB25" s="46"/>
+      <c r="AC25" s="47"/>
+      <c r="AD25" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="11">
@@ -5653,27 +5464,27 @@
       <c r="D26" s="11">
         <v>0</v>
       </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38">
+      <c r="E26" s="36"/>
+      <c r="F26" s="36">
         <v>0</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="35" t="s">
+      <c r="H26" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I26" s="34" t="s">
+      <c r="I26" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J26" s="35" t="s">
+      <c r="J26" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K26" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J26,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L26" s="43" t="s">
+      <c r="L26" s="41" t="s">
         <v>42</v>
       </c>
       <c r="M26" s="11" t="str">
@@ -5692,10 +5503,10 @@
       <c r="Q26" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R26" s="39" t="s">
+      <c r="R26" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S26" s="36">
+      <c r="S26" s="34">
         <v>2</v>
       </c>
       <c r="T26" s="11">
@@ -5705,30 +5516,30 @@
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
       <c r="W26" s="11"/>
-      <c r="X26" s="87"/>
-      <c r="Y26" s="73">
+      <c r="X26" s="46"/>
+      <c r="Y26" s="44">
         <f t="shared" ref="Y26:Y40" si="23">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; U26,U26)</f>
         <v>0</v>
       </c>
-      <c r="Z26" s="73">
+      <c r="Z26" s="44">
         <f t="shared" ref="Z26:Z40" si="24">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V26,V26)</f>
         <v>0</v>
       </c>
-      <c r="AA26" s="73">
+      <c r="AA26" s="44">
         <f t="shared" ref="AA26:AA40" si="25">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; W26,W26)</f>
         <v>0</v>
       </c>
-      <c r="AB26" s="87"/>
-      <c r="AC26" s="88"/>
-      <c r="AD26" s="88" t="s">
+      <c r="AB26" s="46"/>
+      <c r="AC26" s="47"/>
+      <c r="AD26" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="11">
@@ -5737,27 +5548,27 @@
       <c r="D27" s="11">
         <v>0</v>
       </c>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38">
+      <c r="E27" s="36"/>
+      <c r="F27" s="36">
         <v>0</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="35" t="s">
+      <c r="H27" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="34" t="s">
+      <c r="I27" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J27" s="35" t="s">
+      <c r="J27" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K27" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J27,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L27" s="43" t="s">
+      <c r="L27" s="41" t="s">
         <v>42</v>
       </c>
       <c r="M27" s="11" t="str">
@@ -5776,10 +5587,10 @@
       <c r="Q27" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R27" s="39" t="s">
+      <c r="R27" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S27" s="36">
+      <c r="S27" s="34">
         <v>2</v>
       </c>
       <c r="T27" s="11">
@@ -5789,30 +5600,30 @@
       <c r="U27" s="11"/>
       <c r="V27" s="11"/>
       <c r="W27" s="11"/>
-      <c r="X27" s="87"/>
-      <c r="Y27" s="73">
+      <c r="X27" s="46"/>
+      <c r="Y27" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="73">
+      <c r="Z27" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="73">
+      <c r="AA27" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="87"/>
-      <c r="AC27" s="88"/>
-      <c r="AD27" s="88" t="s">
+      <c r="AB27" s="46"/>
+      <c r="AC27" s="47"/>
+      <c r="AD27" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C28" s="11">
@@ -5821,27 +5632,27 @@
       <c r="D28" s="11">
         <v>0</v>
       </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38">
+      <c r="E28" s="36"/>
+      <c r="F28" s="36">
         <v>0</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J28" s="35" t="s">
+      <c r="J28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K28" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J28,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L28" s="43" t="s">
+      <c r="L28" s="41" t="s">
         <v>42</v>
       </c>
       <c r="M28" s="11" t="str">
@@ -5860,10 +5671,10 @@
       <c r="Q28" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R28" s="39" t="s">
+      <c r="R28" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S28" s="36">
+      <c r="S28" s="34">
         <v>2</v>
       </c>
       <c r="T28" s="11">
@@ -5873,30 +5684,30 @@
       <c r="U28" s="11"/>
       <c r="V28" s="11"/>
       <c r="W28" s="11"/>
-      <c r="X28" s="87"/>
-      <c r="Y28" s="73">
+      <c r="X28" s="46"/>
+      <c r="Y28" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="73">
+      <c r="Z28" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="73">
+      <c r="AA28" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="87"/>
-      <c r="AC28" s="88"/>
-      <c r="AD28" s="88" t="s">
+      <c r="AB28" s="46"/>
+      <c r="AC28" s="47"/>
+      <c r="AD28" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="11">
@@ -5905,27 +5716,27 @@
       <c r="D29" s="11">
         <v>0</v>
       </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38">
+      <c r="E29" s="36"/>
+      <c r="F29" s="36">
         <v>0</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H29" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I29" s="34" t="s">
+      <c r="I29" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="35" t="s">
+      <c r="J29" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K29" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J29,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L29" s="60" t="s">
+      <c r="L29" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M29" s="11" t="str">
@@ -5944,10 +5755,10 @@
       <c r="Q29" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R29" s="39" t="s">
+      <c r="R29" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S29" s="36">
+      <c r="S29" s="34">
         <v>2</v>
       </c>
       <c r="T29" s="11">
@@ -5957,30 +5768,30 @@
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
-      <c r="X29" s="87"/>
-      <c r="Y29" s="73">
+      <c r="X29" s="46"/>
+      <c r="Y29" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="73">
+      <c r="Z29" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="73">
+      <c r="AA29" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="87"/>
-      <c r="AC29" s="88"/>
-      <c r="AD29" s="88" t="s">
+      <c r="AB29" s="46"/>
+      <c r="AC29" s="47"/>
+      <c r="AD29" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="11">
@@ -5989,27 +5800,27 @@
       <c r="D30" s="11">
         <v>0</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38">
+      <c r="E30" s="36"/>
+      <c r="F30" s="36">
         <v>0</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H30" s="35" t="s">
+      <c r="H30" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I30" s="34" t="s">
+      <c r="I30" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="35" t="s">
+      <c r="J30" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K30" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J30,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L30" s="60" t="s">
+      <c r="L30" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M30" s="11" t="str">
@@ -6028,10 +5839,10 @@
       <c r="Q30" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R30" s="39" t="s">
+      <c r="R30" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="34">
         <v>2</v>
       </c>
       <c r="T30" s="11">
@@ -6041,30 +5852,30 @@
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
-      <c r="X30" s="87"/>
-      <c r="Y30" s="73">
+      <c r="X30" s="46"/>
+      <c r="Y30" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="73">
+      <c r="Z30" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="73">
+      <c r="AA30" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="87"/>
-      <c r="AC30" s="88"/>
-      <c r="AD30" s="88" t="s">
+      <c r="AB30" s="46"/>
+      <c r="AC30" s="47"/>
+      <c r="AD30" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="11">
@@ -6073,27 +5884,27 @@
       <c r="D31" s="11">
         <v>0</v>
       </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38">
+      <c r="E31" s="36"/>
+      <c r="F31" s="36">
         <v>0</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="35" t="s">
+      <c r="H31" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I31" s="34" t="s">
+      <c r="I31" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J31" s="35" t="s">
+      <c r="J31" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K31" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J31,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L31" s="60" t="s">
+      <c r="L31" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M31" s="11" t="str">
@@ -6112,10 +5923,10 @@
       <c r="Q31" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R31" s="39" t="s">
+      <c r="R31" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S31" s="36">
+      <c r="S31" s="34">
         <v>2</v>
       </c>
       <c r="T31" s="11">
@@ -6125,30 +5936,30 @@
       <c r="U31" s="11"/>
       <c r="V31" s="11"/>
       <c r="W31" s="11"/>
-      <c r="X31" s="87"/>
-      <c r="Y31" s="73">
+      <c r="X31" s="46"/>
+      <c r="Y31" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z31" s="73">
+      <c r="Z31" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA31" s="73">
+      <c r="AA31" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB31" s="87"/>
-      <c r="AC31" s="88"/>
-      <c r="AD31" s="88" t="s">
+      <c r="AB31" s="46"/>
+      <c r="AC31" s="47"/>
+      <c r="AD31" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C32" s="11">
@@ -6157,27 +5968,27 @@
       <c r="D32" s="11">
         <v>0</v>
       </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38">
+      <c r="E32" s="36"/>
+      <c r="F32" s="36">
         <v>0</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I32" s="34" t="s">
+      <c r="I32" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J32" s="35" t="s">
+      <c r="J32" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J32,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L32" s="60" t="s">
+      <c r="L32" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M32" s="11" t="str">
@@ -6196,10 +6007,10 @@
       <c r="Q32" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R32" s="39" t="s">
+      <c r="R32" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S32" s="36">
+      <c r="S32" s="34">
         <v>2</v>
       </c>
       <c r="T32" s="11">
@@ -6209,30 +6020,30 @@
       <c r="U32" s="11"/>
       <c r="V32" s="11"/>
       <c r="W32" s="11"/>
-      <c r="X32" s="87"/>
-      <c r="Y32" s="73">
+      <c r="X32" s="46"/>
+      <c r="Y32" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z32" s="73">
+      <c r="Z32" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA32" s="73">
+      <c r="AA32" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB32" s="87"/>
-      <c r="AC32" s="88"/>
-      <c r="AD32" s="88" t="s">
+      <c r="AB32" s="46"/>
+      <c r="AC32" s="47"/>
+      <c r="AD32" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C33" s="11">
@@ -6241,27 +6052,27 @@
       <c r="D33" s="11">
         <v>0</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38">
+      <c r="E33" s="36"/>
+      <c r="F33" s="36">
         <v>0</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="35" t="s">
+      <c r="H33" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I33" s="34" t="s">
+      <c r="I33" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J33" s="35" t="s">
+      <c r="J33" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K33" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J33,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L33" s="60" t="s">
+      <c r="L33" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M33" s="11" t="str">
@@ -6280,10 +6091,10 @@
       <c r="Q33" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R33" s="39" t="s">
+      <c r="R33" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S33" s="36">
+      <c r="S33" s="34">
         <v>2</v>
       </c>
       <c r="T33" s="11">
@@ -6293,30 +6104,30 @@
       <c r="U33" s="11"/>
       <c r="V33" s="11"/>
       <c r="W33" s="11"/>
-      <c r="X33" s="87"/>
-      <c r="Y33" s="73">
+      <c r="X33" s="46"/>
+      <c r="Y33" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z33" s="73">
+      <c r="Z33" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA33" s="73">
+      <c r="AA33" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB33" s="87"/>
-      <c r="AC33" s="88"/>
-      <c r="AD33" s="88" t="s">
+      <c r="AB33" s="46"/>
+      <c r="AC33" s="47"/>
+      <c r="AD33" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="11">
@@ -6325,27 +6136,27 @@
       <c r="D34" s="11">
         <v>0</v>
       </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38">
+      <c r="E34" s="36"/>
+      <c r="F34" s="36">
         <v>0</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H34" s="35" t="s">
+      <c r="H34" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I34" s="34" t="s">
+      <c r="I34" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J34" s="35" t="s">
+      <c r="J34" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K34" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J34,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L34" s="60" t="s">
+      <c r="L34" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M34" s="11" t="str">
@@ -6364,10 +6175,10 @@
       <c r="Q34" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R34" s="39" t="s">
+      <c r="R34" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S34" s="36">
+      <c r="S34" s="34">
         <v>2</v>
       </c>
       <c r="T34" s="11">
@@ -6377,30 +6188,30 @@
       <c r="U34" s="11"/>
       <c r="V34" s="11"/>
       <c r="W34" s="11"/>
-      <c r="X34" s="87"/>
-      <c r="Y34" s="73">
+      <c r="X34" s="46"/>
+      <c r="Y34" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z34" s="73">
+      <c r="Z34" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA34" s="73">
+      <c r="AA34" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB34" s="87"/>
-      <c r="AC34" s="88"/>
-      <c r="AD34" s="88" t="s">
+      <c r="AB34" s="46"/>
+      <c r="AC34" s="47"/>
+      <c r="AD34" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C35" s="11">
@@ -6409,27 +6220,27 @@
       <c r="D35" s="11">
         <v>0</v>
       </c>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38">
+      <c r="E35" s="36"/>
+      <c r="F35" s="36">
         <v>0</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H35" s="35" t="s">
+      <c r="H35" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I35" s="34" t="s">
+      <c r="I35" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J35" s="35" t="s">
+      <c r="J35" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K35" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J35,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L35" s="60" t="s">
+      <c r="L35" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M35" s="11" t="str">
@@ -6448,10 +6259,10 @@
       <c r="Q35" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R35" s="39" t="s">
+      <c r="R35" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S35" s="36">
+      <c r="S35" s="34">
         <v>2</v>
       </c>
       <c r="T35" s="11">
@@ -6461,30 +6272,30 @@
       <c r="U35" s="11"/>
       <c r="V35" s="11"/>
       <c r="W35" s="11"/>
-      <c r="X35" s="87"/>
-      <c r="Y35" s="73">
+      <c r="X35" s="46"/>
+      <c r="Y35" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z35" s="73">
+      <c r="Z35" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA35" s="73">
+      <c r="AA35" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB35" s="87"/>
-      <c r="AC35" s="88"/>
-      <c r="AD35" s="88" t="s">
+      <c r="AB35" s="46"/>
+      <c r="AC35" s="47"/>
+      <c r="AD35" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C36" s="11">
@@ -6493,27 +6304,27 @@
       <c r="D36" s="11">
         <v>0</v>
       </c>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38">
+      <c r="E36" s="36"/>
+      <c r="F36" s="36">
         <v>0</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H36" s="35" t="s">
+      <c r="H36" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I36" s="34" t="s">
+      <c r="I36" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J36" s="35" t="s">
+      <c r="J36" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K36" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J36,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L36" s="60" t="s">
+      <c r="L36" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M36" s="11" t="str">
@@ -6532,10 +6343,10 @@
       <c r="Q36" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R36" s="39" t="s">
+      <c r="R36" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S36" s="36">
+      <c r="S36" s="34">
         <v>2</v>
       </c>
       <c r="T36" s="11">
@@ -6545,30 +6356,30 @@
       <c r="U36" s="11"/>
       <c r="V36" s="11"/>
       <c r="W36" s="11"/>
-      <c r="X36" s="87"/>
-      <c r="Y36" s="73">
+      <c r="X36" s="46"/>
+      <c r="Y36" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="73">
+      <c r="Z36" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="73">
+      <c r="AA36" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="87"/>
-      <c r="AC36" s="88"/>
-      <c r="AD36" s="88" t="s">
+      <c r="AB36" s="46"/>
+      <c r="AC36" s="47"/>
+      <c r="AD36" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C37" s="11">
@@ -6577,27 +6388,27 @@
       <c r="D37" s="11">
         <v>0</v>
       </c>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38">
+      <c r="E37" s="36"/>
+      <c r="F37" s="36">
         <v>0</v>
       </c>
       <c r="G37" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H37" s="35" t="s">
+      <c r="H37" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I37" s="34" t="s">
+      <c r="I37" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J37" s="35" t="s">
+      <c r="J37" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K37" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J37,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L37" s="60" t="s">
+      <c r="L37" s="33" t="s">
         <v>69</v>
       </c>
       <c r="M37" s="11" t="str">
@@ -6616,10 +6427,10 @@
       <c r="Q37" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R37" s="39" t="s">
+      <c r="R37" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S37" s="36">
+      <c r="S37" s="34">
         <v>2</v>
       </c>
       <c r="T37" s="11">
@@ -6629,30 +6440,30 @@
       <c r="U37" s="11"/>
       <c r="V37" s="11"/>
       <c r="W37" s="11"/>
-      <c r="X37" s="87"/>
-      <c r="Y37" s="73">
+      <c r="X37" s="46"/>
+      <c r="Y37" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z37" s="73">
+      <c r="Z37" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA37" s="73">
+      <c r="AA37" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="87"/>
-      <c r="AC37" s="88"/>
-      <c r="AD37" s="88" t="s">
+      <c r="AB37" s="46"/>
+      <c r="AC37" s="47"/>
+      <c r="AD37" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C38" s="11">
@@ -6661,27 +6472,27 @@
       <c r="D38" s="11">
         <v>0</v>
       </c>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38">
+      <c r="E38" s="36"/>
+      <c r="F38" s="36">
         <v>0</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="35" t="s">
+      <c r="H38" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I38" s="34" t="s">
+      <c r="I38" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J38" s="35" t="s">
+      <c r="J38" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K38" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J38,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L38" s="80" t="s">
+      <c r="L38" s="41" t="s">
         <v>51</v>
       </c>
       <c r="M38" s="11" t="str">
@@ -6700,10 +6511,10 @@
       <c r="Q38" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R38" s="39" t="s">
+      <c r="R38" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S38" s="36">
+      <c r="S38" s="34">
         <v>2</v>
       </c>
       <c r="T38" s="11">
@@ -6713,30 +6524,30 @@
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
       <c r="W38" s="11"/>
-      <c r="X38" s="87"/>
-      <c r="Y38" s="73">
+      <c r="X38" s="46"/>
+      <c r="Y38" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z38" s="73">
+      <c r="Z38" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA38" s="73">
+      <c r="AA38" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB38" s="87"/>
-      <c r="AC38" s="88"/>
-      <c r="AD38" s="88" t="s">
+      <c r="AB38" s="46"/>
+      <c r="AC38" s="47"/>
+      <c r="AD38" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C39" s="11">
@@ -6745,27 +6556,27 @@
       <c r="D39" s="11">
         <v>0</v>
       </c>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38">
+      <c r="E39" s="36"/>
+      <c r="F39" s="36">
         <v>0</v>
       </c>
       <c r="G39" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H39" s="35" t="s">
+      <c r="H39" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I39" s="34" t="s">
+      <c r="I39" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J39" s="35" t="s">
+      <c r="J39" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K39" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J39,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L39" s="80" t="s">
+      <c r="L39" s="41" t="s">
         <v>51</v>
       </c>
       <c r="M39" s="11" t="str">
@@ -6784,10 +6595,10 @@
       <c r="Q39" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R39" s="39" t="s">
+      <c r="R39" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S39" s="36">
+      <c r="S39" s="34">
         <v>2</v>
       </c>
       <c r="T39" s="11">
@@ -6797,30 +6608,30 @@
       <c r="U39" s="11"/>
       <c r="V39" s="11"/>
       <c r="W39" s="11"/>
-      <c r="X39" s="87"/>
-      <c r="Y39" s="73">
+      <c r="X39" s="46"/>
+      <c r="Y39" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z39" s="73">
+      <c r="Z39" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA39" s="73">
+      <c r="AA39" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB39" s="87"/>
-      <c r="AC39" s="88"/>
-      <c r="AD39" s="88" t="s">
+      <c r="AB39" s="46"/>
+      <c r="AC39" s="47"/>
+      <c r="AD39" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="30" t="s">
+      <c r="A40" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C40" s="11">
@@ -6829,27 +6640,27 @@
       <c r="D40" s="11">
         <v>0</v>
       </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38">
+      <c r="E40" s="36"/>
+      <c r="F40" s="36">
         <v>0</v>
       </c>
       <c r="G40" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H40" s="35" t="s">
+      <c r="H40" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I40" s="34" t="s">
+      <c r="I40" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J40" s="35" t="s">
+      <c r="J40" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K40" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J40,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L40" s="35" t="s">
+      <c r="L40" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M40" s="11" t="str">
@@ -6868,10 +6679,10 @@
       <c r="Q40" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R40" s="39" t="s">
+      <c r="R40" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S40" s="36">
+      <c r="S40" s="34">
         <v>2</v>
       </c>
       <c r="T40" s="11">
@@ -6881,30 +6692,30 @@
       <c r="U40" s="11"/>
       <c r="V40" s="11"/>
       <c r="W40" s="11"/>
-      <c r="X40" s="87"/>
-      <c r="Y40" s="73">
+      <c r="X40" s="46"/>
+      <c r="Y40" s="44">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Z40" s="73">
+      <c r="Z40" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AA40" s="73">
+      <c r="AA40" s="44">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB40" s="87"/>
-      <c r="AC40" s="88"/>
-      <c r="AD40" s="88" t="s">
+      <c r="AB40" s="46"/>
+      <c r="AC40" s="47"/>
+      <c r="AD40" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C41" s="11">
@@ -6913,27 +6724,27 @@
       <c r="D41" s="11">
         <v>0</v>
       </c>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38">
+      <c r="E41" s="36"/>
+      <c r="F41" s="36">
         <v>0</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H41" s="35" t="s">
+      <c r="H41" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I41" s="34" t="s">
+      <c r="I41" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J41" s="35" t="s">
+      <c r="J41" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K41" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J41,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L41" s="35" t="s">
+      <c r="L41" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M41" s="11" t="str">
@@ -6952,10 +6763,10 @@
       <c r="Q41" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R41" s="39" t="s">
+      <c r="R41" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S41" s="36">
+      <c r="S41" s="34">
         <v>2</v>
       </c>
       <c r="T41" s="11">
@@ -6965,30 +6776,30 @@
       <c r="U41" s="11"/>
       <c r="V41" s="11"/>
       <c r="W41" s="11"/>
-      <c r="X41" s="87"/>
-      <c r="Y41" s="73">
+      <c r="X41" s="46"/>
+      <c r="Y41" s="44">
         <f t="shared" ref="Y41:Y46" si="26">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; U41,U41)</f>
         <v>0</v>
       </c>
-      <c r="Z41" s="73">
+      <c r="Z41" s="44">
         <f t="shared" ref="Z41:Z46" si="27">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; V41,V41)</f>
         <v>0</v>
       </c>
-      <c r="AA41" s="73">
+      <c r="AA41" s="44">
         <f t="shared" ref="AA41:AA46" si="28">HYPERLINK("https://tkebrasil.atlassian.net/browse/" &amp; W41,W41)</f>
         <v>0</v>
       </c>
-      <c r="AB41" s="87"/>
-      <c r="AC41" s="88"/>
-      <c r="AD41" s="88" t="s">
+      <c r="AB41" s="46"/>
+      <c r="AC41" s="47"/>
+      <c r="AD41" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C42" s="11">
@@ -6997,27 +6808,27 @@
       <c r="D42" s="11">
         <v>0</v>
       </c>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38">
+      <c r="E42" s="36"/>
+      <c r="F42" s="36">
         <v>0</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H42" s="35" t="s">
+      <c r="H42" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I42" s="34" t="s">
+      <c r="I42" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J42" s="35" t="s">
+      <c r="J42" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K42" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J42,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L42" s="35" t="s">
+      <c r="L42" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M42" s="11" t="str">
@@ -7036,10 +6847,10 @@
       <c r="Q42" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R42" s="39" t="s">
+      <c r="R42" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S42" s="36">
+      <c r="S42" s="34">
         <v>2</v>
       </c>
       <c r="T42" s="11">
@@ -7049,30 +6860,30 @@
       <c r="U42" s="11"/>
       <c r="V42" s="11"/>
       <c r="W42" s="11"/>
-      <c r="X42" s="87"/>
-      <c r="Y42" s="73">
+      <c r="X42" s="46"/>
+      <c r="Y42" s="44">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z42" s="73">
+      <c r="Z42" s="44">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="73">
+      <c r="AA42" s="44">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="87"/>
-      <c r="AC42" s="88"/>
-      <c r="AD42" s="88" t="s">
+      <c r="AB42" s="46"/>
+      <c r="AC42" s="47"/>
+      <c r="AD42" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C43" s="11">
@@ -7081,27 +6892,27 @@
       <c r="D43" s="11">
         <v>0</v>
       </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38">
+      <c r="E43" s="36"/>
+      <c r="F43" s="36">
         <v>0</v>
       </c>
       <c r="G43" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="35" t="s">
+      <c r="H43" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I43" s="34" t="s">
+      <c r="I43" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J43" s="35" t="s">
+      <c r="J43" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K43" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J43,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L43" s="35" t="s">
+      <c r="L43" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M43" s="11" t="str">
@@ -7120,10 +6931,10 @@
       <c r="Q43" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R43" s="39" t="s">
+      <c r="R43" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S43" s="36">
+      <c r="S43" s="34">
         <v>2</v>
       </c>
       <c r="T43" s="11">
@@ -7133,30 +6944,30 @@
       <c r="U43" s="11"/>
       <c r="V43" s="11"/>
       <c r="W43" s="11"/>
-      <c r="X43" s="87"/>
-      <c r="Y43" s="73">
+      <c r="X43" s="46"/>
+      <c r="Y43" s="44">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z43" s="73">
+      <c r="Z43" s="44">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AA43" s="73">
+      <c r="AA43" s="44">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AB43" s="87"/>
-      <c r="AC43" s="88"/>
-      <c r="AD43" s="88" t="s">
+      <c r="AB43" s="46"/>
+      <c r="AC43" s="47"/>
+      <c r="AD43" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C44" s="11">
@@ -7165,27 +6976,27 @@
       <c r="D44" s="11">
         <v>0</v>
       </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38">
+      <c r="E44" s="36"/>
+      <c r="F44" s="36">
         <v>0</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H44" s="35" t="s">
+      <c r="H44" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I44" s="34" t="s">
+      <c r="I44" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J44" s="35" t="s">
+      <c r="J44" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K44" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J44,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L44" s="35" t="s">
+      <c r="L44" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M44" s="11" t="str">
@@ -7204,10 +7015,10 @@
       <c r="Q44" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R44" s="39" t="s">
+      <c r="R44" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S44" s="36">
+      <c r="S44" s="34">
         <v>2</v>
       </c>
       <c r="T44" s="11">
@@ -7217,30 +7028,30 @@
       <c r="U44" s="11"/>
       <c r="V44" s="11"/>
       <c r="W44" s="11"/>
-      <c r="X44" s="87"/>
-      <c r="Y44" s="73">
+      <c r="X44" s="46"/>
+      <c r="Y44" s="44">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z44" s="73">
+      <c r="Z44" s="44">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AA44" s="73">
+      <c r="AA44" s="44">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AB44" s="87"/>
-      <c r="AC44" s="88"/>
-      <c r="AD44" s="88" t="s">
+      <c r="AB44" s="46"/>
+      <c r="AC44" s="47"/>
+      <c r="AD44" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C45" s="11">
@@ -7249,27 +7060,27 @@
       <c r="D45" s="11">
         <v>0</v>
       </c>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38">
+      <c r="E45" s="36"/>
+      <c r="F45" s="36">
         <v>0</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="35" t="s">
+      <c r="H45" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="34" t="s">
+      <c r="I45" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J45" s="35" t="s">
+      <c r="J45" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K45" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J45,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L45" s="35" t="s">
+      <c r="L45" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M45" s="11" t="str">
@@ -7288,10 +7099,10 @@
       <c r="Q45" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R45" s="39" t="s">
+      <c r="R45" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S45" s="36">
+      <c r="S45" s="34">
         <v>2</v>
       </c>
       <c r="T45" s="11">
@@ -7301,30 +7112,30 @@
       <c r="U45" s="11"/>
       <c r="V45" s="11"/>
       <c r="W45" s="11"/>
-      <c r="X45" s="87"/>
-      <c r="Y45" s="73">
+      <c r="X45" s="46"/>
+      <c r="Y45" s="44">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z45" s="73">
+      <c r="Z45" s="44">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AA45" s="73">
+      <c r="AA45" s="44">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AB45" s="87"/>
-      <c r="AC45" s="88"/>
-      <c r="AD45" s="88" t="s">
+      <c r="AB45" s="46"/>
+      <c r="AC45" s="47"/>
+      <c r="AD45" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="30" t="s">
+      <c r="A46" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C46" s="11">
@@ -7333,27 +7144,27 @@
       <c r="D46" s="11">
         <v>0</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38">
+      <c r="E46" s="36"/>
+      <c r="F46" s="36">
         <v>0</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="35" t="s">
+      <c r="H46" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="I46" s="34" t="s">
+      <c r="I46" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J46" s="35" t="s">
+      <c r="J46" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K46" s="11" t="str">
         <f>_xlfn.XLOOKUP(Planilha!$J46,Tabela9[Pessoas],Tabela9[UUID Jira])</f>
         <v>712020:8364b9cf-88a2-4399-9f86-fff7bed77ce2</v>
       </c>
-      <c r="L46" s="35" t="s">
+      <c r="L46" s="33" t="s">
         <v>59</v>
       </c>
       <c r="M46" s="11" t="str">
@@ -7372,10 +7183,10 @@
       <c r="Q46" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R46" s="39" t="s">
+      <c r="R46" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="S46" s="36">
+      <c r="S46" s="34">
         <v>2</v>
       </c>
       <c r="T46" s="11">
@@ -7385,22 +7196,22 @@
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
       <c r="W46" s="11"/>
-      <c r="X46" s="87"/>
-      <c r="Y46" s="73">
+      <c r="X46" s="46"/>
+      <c r="Y46" s="44">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z46" s="73">
+      <c r="Z46" s="44">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AA46" s="73">
+      <c r="AA46" s="44">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AB46" s="87"/>
-      <c r="AC46" s="88"/>
-      <c r="AD46" s="88" t="s">
+      <c r="AB46" s="46"/>
+      <c r="AC46" s="47"/>
+      <c r="AD46" s="47" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7476,27 +7287,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="61"/>
-      <c r="C2" s="94" t="str">
-        <f>Parâmetros!$I3</f>
+      <c r="B2" s="42"/>
+      <c r="C2" s="49" t="str">
+        <f>Parâmetros!$J3</f>
         <v>BL</v>
       </c>
-      <c r="D2" s="95" t="str">
-        <f>Parâmetros!$I4</f>
+      <c r="D2" s="50" t="str">
+        <f>Parâmetros!$J4</f>
         <v>CR</v>
       </c>
-      <c r="E2" s="95" t="str">
-        <f>Parâmetros!$I5</f>
+      <c r="E2" s="50" t="str">
+        <f>Parâmetros!$J5</f>
         <v>MP</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="54" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="13">
@@ -7511,38 +7322,38 @@
         <f>SUMIF(Planilha!$AD$2:$AD$2968,E2,Planilha!$S$2:$S$2968)</f>
         <v>1</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="79">
         <f>SUM(Planilha!S2:S2968)</f>
         <v>151</v>
       </c>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
     </row>
     <row r="4" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="14">
         <f>SUMIF(Planilha!$AD$2:$AD$2968,C2,Planilha!$T$2:$T$2968)</f>
         <v>24</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="14">
         <f>SUMIF(Planilha!$AD$2:$AD$2968,D2,Planilha!$T$2:$T$2968)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="14">
         <f>SUMIF(Planilha!$AD$2:$AD$2968,E2,Planilha!$T$2:$T$2968)</f>
         <v>0.5</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="80">
         <f>SUM(Planilha!T2:T2968)</f>
         <v>25.5</v>
       </c>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
     </row>
     <row r="5" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="55" t="s">
         <v>190</v>
       </c>
       <c r="C5" s="13">
@@ -7557,15 +7368,15 @@
         <f>COUNTA(_xlfn.UNIQUE(Planilha!AG2:AG2968))-2</f>
         <v>1</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="79">
         <f>COUNTA(_xlfn.UNIQUE(Planilha!U2:U2968))-1</f>
         <v>17</v>
       </c>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
     </row>
     <row r="6" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="106" t="s">
+      <c r="B6" s="55" t="s">
         <v>191</v>
       </c>
       <c r="C6" s="13">
@@ -7580,15 +7391,15 @@
         <f>COUNTA(_xlfn.UNIQUE(Planilha!AJ2:AJ2968))-2</f>
         <v>1</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="79">
         <f>COUNTA(_xlfn.UNIQUE(Planilha!V2:V2968))-1</f>
         <v>0</v>
       </c>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
     </row>
     <row r="7" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="107" t="s">
+      <c r="B7" s="56" t="s">
         <v>192</v>
       </c>
       <c r="C7" s="13">
@@ -7603,49 +7414,49 @@
         <f>COUNTA(_xlfn.UNIQUE(Planilha!AM2:AM2968))-2</f>
         <v>1</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="79">
         <f>COUNTA(_xlfn.UNIQUE(Planilha!W2:W2968))-1</f>
         <v>0</v>
       </c>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
     </row>
     <row r="8" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="92"/>
-      <c r="C8" s="97" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="66" t="s">
         <v>193</v>
       </c>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98" t="s">
+      <c r="D8" s="58"/>
+      <c r="E8" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="F8" s="98"/>
-      <c r="G8" s="99" t="s">
+      <c r="F8" s="58"/>
+      <c r="G8" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="100" t="s">
+      <c r="H8" s="64" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="93"/>
-      <c r="C9" s="101" t="s">
+      <c r="B9" s="61"/>
+      <c r="C9" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="102" t="s">
+      <c r="D9" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="102" t="s">
+      <c r="E9" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="102" t="s">
+      <c r="F9" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="103"/>
-      <c r="H9" s="104"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="108" t="str">
+      <c r="B10" s="57" t="str">
         <f>Parâmetros!F3</f>
         <v>Alexandre Trindade Pereira</v>
       </c>
@@ -7653,7 +7464,7 @@
         <f>SUMIFS(Planilha!$S$2:$S$2968,Planilha!$L$2:$L$2968,B10,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>10</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <f>SUMIFS(Planilha!$T$2:$T$2968,Planilha!$L$2:$L$2968,B10,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>1</v>
       </c>
@@ -7661,21 +7472,21 @@
         <f>G10-C10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <f>H10-D10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="79">
         <f>SUMIF(Planilha!$L$2:$L$2968,B10,Planilha!$S$2:$S$2968)</f>
         <v>10</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="80">
         <f>SUMIF(Planilha!$L$2:$L$2968,B10,Planilha!$T$2:$T$2968)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="106" t="str">
+      <c r="B11" s="55" t="str">
         <f>Parâmetros!F4</f>
         <v>Giovani Perotto Mesquita</v>
       </c>
@@ -7683,7 +7494,7 @@
         <f>SUMIFS(Planilha!$S$2:$S$2968,Planilha!$L$2:$L$2968,B11,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>0</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="14">
         <f>SUMIFS(Planilha!$T$2:$T$2968,Planilha!$L$2:$L$2968,B11,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>0</v>
       </c>
@@ -7691,21 +7502,21 @@
         <f t="shared" ref="E11:E17" si="0">G11-C11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <f t="shared" ref="F11:F17" si="1">H11-D11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="79">
         <f>SUMIF(Planilha!$L$2:$L$2968,B11,Planilha!$S$2:$S$2968)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="80">
         <f>SUMIF(Planilha!$L$2:$L$2968,B11,Planilha!$T$2:$T$2968)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="106" t="str">
+      <c r="B12" s="55" t="str">
         <f>Parâmetros!F5</f>
         <v>Luis Henrique Petkovicz</v>
       </c>
@@ -7713,7 +7524,7 @@
         <f>SUMIFS(Planilha!$S$2:$S$2968,Planilha!$L$2:$L$2968,B12,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>28</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <f>SUMIFS(Planilha!$T$2:$T$2968,Planilha!$L$2:$L$2968,B12,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>3</v>
       </c>
@@ -7721,21 +7532,21 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="79">
         <f>SUMIF(Planilha!$L$2:$L$2968,B12,Planilha!$S$2:$S$2968)</f>
         <v>38</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="80">
         <f>SUMIF(Planilha!$L$2:$L$2968,B12,Planilha!$T$2:$T$2968)</f>
         <v>5.5</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="106" t="str">
+      <c r="B13" s="55" t="str">
         <f>Parâmetros!F6</f>
         <v>Luiz Felipe Brandão da Silva</v>
       </c>
@@ -7743,7 +7554,7 @@
         <f>SUMIFS(Planilha!$S$2:$S$2968,Planilha!$L$2:$L$2968,B13,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>16</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <f>SUMIFS(Planilha!$T$2:$T$2968,Planilha!$L$2:$L$2968,B13,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>2.5</v>
       </c>
@@ -7751,21 +7562,21 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="79">
         <f>SUMIF(Planilha!$L$2:$L$2968,B13,Planilha!$S$2:$S$2968)</f>
         <v>34</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="80">
         <f>SUMIF(Planilha!$L$2:$L$2968,B13,Planilha!$T$2:$T$2968)</f>
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="106" t="str">
+      <c r="B14" s="55" t="str">
         <f>Parâmetros!F7</f>
         <v>Pablo Rocha</v>
       </c>
@@ -7773,7 +7584,7 @@
         <f>SUMIFS(Planilha!$S$2:$S$2968,Planilha!$L$2:$L$2968,B14,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>26</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f>SUMIFS(Planilha!$T$2:$T$2968,Planilha!$L$2:$L$2968,B14,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>3.5</v>
       </c>
@@ -7781,21 +7592,21 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="79">
         <f>SUMIF(Planilha!$L$2:$L$2968,B14,Planilha!$S$2:$S$2968)</f>
         <v>30</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="80">
         <f>SUMIF(Planilha!$L$2:$L$2968,B14,Planilha!$T$2:$T$2968)</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="106" t="str">
+      <c r="B15" s="55" t="str">
         <f>Parâmetros!F8</f>
         <v>Regina Albanus</v>
       </c>
@@ -7803,7 +7614,7 @@
         <f>SUMIFS(Planilha!$S$2:$S$2968,Planilha!$L$2:$L$2968,B15,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>24</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <f>SUMIFS(Planilha!$T$2:$T$2968,Planilha!$L$2:$L$2968,B15,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>3.5</v>
       </c>
@@ -7811,21 +7622,21 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="79">
         <f>SUMIF(Planilha!$L$2:$L$2968,B15,Planilha!$S$2:$S$2968)</f>
         <v>38</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="80">
         <f>SUMIF(Planilha!$L$2:$L$2968,B15,Planilha!$T$2:$T$2968)</f>
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="106" t="str">
+      <c r="B16" s="55" t="str">
         <f>Parâmetros!F9</f>
         <v>Stephanie Oliveira</v>
       </c>
@@ -7833,7 +7644,7 @@
         <f>SUMIFS(Planilha!$S$2:$S$2968,Planilha!$L$2:$L$2968,B16,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>0</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <f>SUMIFS(Planilha!$T$2:$T$2968,Planilha!$L$2:$L$2968,B16,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>0</v>
       </c>
@@ -7841,21 +7652,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="79">
         <f>SUMIF(Planilha!$L$2:$L$2968,B16,Planilha!$S$2:$S$2968)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="80">
         <f>SUMIF(Planilha!$L$2:$L$2968,B16,Planilha!$T$2:$T$2968)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="107" t="str">
+      <c r="B17" s="56" t="str">
         <f>Parâmetros!F10</f>
         <v>Tanise Sarmento</v>
       </c>
@@ -7863,7 +7674,7 @@
         <f>SUMIFS(Planilha!$S$2:$S$2968,Planilha!$L$2:$L$2968,B17,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>1</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <f>SUMIFS(Planilha!$T$2:$T$2968,Planilha!$L$2:$L$2968,B17,Planilha!$AC$2:$AC$2968,"X")</f>
         <v>0.5</v>
       </c>
@@ -7871,42 +7682,42 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="79">
         <f>SUMIF(Planilha!$L$2:$L$2968,B17,Planilha!$S$2:$S$2968)</f>
         <v>1</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="80">
         <f>SUMIF(Planilha!$L$2:$L$2968,B17,Planilha!$T$2:$T$2968)</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="8"/>
-      <c r="C18" s="14">
+      <c r="C18" s="79">
         <f>SUM(C10:C17)</f>
         <v>105</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="80">
         <f t="shared" ref="D18" si="2">SUM(D10:D17)</f>
         <v>14</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="79">
         <f t="shared" ref="E18" si="3">SUM(E10:E17)</f>
         <v>46</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="80">
         <f t="shared" ref="F18" si="4">SUM(F10:F17)</f>
         <v>11.5</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="77">
         <f>SUM(G10:G17)</f>
         <v>151</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="78">
         <f>SUM(H10:H17)</f>
         <v>25.5</v>
       </c>
@@ -7926,7 +7737,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:M12"/>
+  <dimension ref="B2:N12"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.33203125" customWidth="1"/>
@@ -7934,17 +7745,18 @@
     <col min="3" max="3" width="2.33203125" customWidth="1"/>
     <col min="4" max="4" width="19.6640625" customWidth="1"/>
     <col min="5" max="5" width="2.33203125" customWidth="1"/>
-    <col min="6" max="6" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.33203125" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.33203125" customWidth="1"/>
-    <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.21875" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.33203125" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.33203125" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>195</v>
       </c>
@@ -7955,22 +7767,25 @@
         <v>197</v>
       </c>
       <c r="G2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2" t="s">
         <v>198</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>199</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>200</v>
       </c>
-      <c r="L2" s="109" t="s">
+      <c r="M2" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="109" t="s">
+      <c r="N2" s="74" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>38</v>
       </c>
@@ -7981,22 +7796,25 @@
         <v>30</v>
       </c>
       <c r="G3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H3" t="s">
         <v>202</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>45</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>203</v>
       </c>
-      <c r="L3" s="112">
+      <c r="M3" s="75">
         <v>7.9</v>
       </c>
-      <c r="M3" s="110">
+      <c r="N3" s="76">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
@@ -8007,22 +7825,25 @@
         <v>29</v>
       </c>
       <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
         <v>204</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>35</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>205</v>
       </c>
-      <c r="L4" s="112">
+      <c r="M4" s="75">
         <v>23.9</v>
       </c>
-      <c r="M4" s="110">
+      <c r="N4" s="76">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>206</v>
       </c>
@@ -8033,22 +7854,25 @@
         <v>42</v>
       </c>
       <c r="G5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H5" t="s">
         <v>207</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>41</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>208</v>
       </c>
-      <c r="L5" s="112">
+      <c r="M5" s="75">
         <v>39.9</v>
       </c>
-      <c r="M5" s="110">
+      <c r="N5" s="76">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>209</v>
       </c>
@@ -8059,16 +7883,19 @@
         <v>69</v>
       </c>
       <c r="G6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H6" t="s">
         <v>211</v>
       </c>
-      <c r="L6" s="112">
+      <c r="M6" s="75">
         <v>59.9</v>
       </c>
-      <c r="M6" s="110">
+      <c r="N6" s="76">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="D7" s="2" t="s">
         <v>212</v>
       </c>
@@ -8076,16 +7903,19 @@
         <v>51</v>
       </c>
       <c r="G7" t="s">
+        <v>224</v>
+      </c>
+      <c r="H7" t="s">
         <v>213</v>
       </c>
-      <c r="L7" s="112">
+      <c r="M7" s="75">
         <v>79.900000000000006</v>
       </c>
-      <c r="M7" s="110">
+      <c r="N7" s="76">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="D8" s="2" t="s">
         <v>79</v>
       </c>
@@ -8093,16 +7923,19 @@
         <v>59</v>
       </c>
       <c r="G8" t="s">
+        <v>224</v>
+      </c>
+      <c r="H8" t="s">
         <v>214</v>
       </c>
-      <c r="L8" s="113">
+      <c r="M8" s="75">
         <v>99.9</v>
       </c>
-      <c r="M8" s="110">
+      <c r="N8" s="76">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="2" t="s">
         <v>215</v>
       </c>
@@ -8110,16 +7943,19 @@
         <v>216</v>
       </c>
       <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
         <v>217</v>
       </c>
-      <c r="L9" s="113">
+      <c r="M9" s="75">
         <v>9999</v>
       </c>
-      <c r="M9" s="111">
+      <c r="N9" s="76">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D10" s="2" t="s">
         <v>218</v>
       </c>
@@ -8127,15 +7963,18 @@
         <v>39</v>
       </c>
       <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="D11" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="D12" s="3" t="s">
         <v>221</v>
       </c>
@@ -8153,15 +7992,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003AA76C533D05464883196520997177C7" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="611b75a091fa37ff9f3d4026e297cc72">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c2c9c08b-70d6-43f3-aae5-2f0bb20324a0" xmlns:ns3="a8b8c1e4-87a1-4b14-958b-2719ee40e95e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bc29f8ee4ef08b3b822c48c3e9bd53fd" ns2:_="" ns3:_="">
     <xsd:import namespace="c2c9c08b-70d6-43f3-aae5-2f0bb20324a0"/>
@@ -8396,6 +8226,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8408,14 +8247,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E919BE6-D80F-4619-B0D1-AE4CBF4A13AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D029D4D6-D43A-4EE6-9C29-383488773521}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8430,6 +8261,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E919BE6-D80F-4619-B0D1-AE4CBF4A13AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
